--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787943</v>
+        <v>128787957</v>
       </c>
       <c r="B2" t="n">
-        <v>90290</v>
+        <v>92761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752782</v>
+        <v>752711</v>
       </c>
       <c r="R2" t="n">
-        <v>7094651</v>
+        <v>7094778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>92760</v>
+        <v>90290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +886,7 @@
         <v>128787996</v>
       </c>
       <c r="B4" t="n">
-        <v>91627</v>
+        <v>91628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R7" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R8" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92786</v>
+        <v>92761</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92760</v>
+        <v>92787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R13" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R15" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787966</v>
+        <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752758</v>
+        <v>752787</v>
       </c>
       <c r="R16" t="n">
-        <v>7094712</v>
+        <v>7094681</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>92761</v>
+        <v>91655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R2" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,7 +800,7 @@
         <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
+        <v>92788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R4" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128787945</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92787</v>
+        <v>92814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2450,6 +2450,963 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128815360</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>752738</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7094815</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>tunn tallgren nedsänkt i mossa</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128815362</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>752811</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7094687</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>silverlåga nedbruten delvis</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128815356</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92810</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>752793</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7094748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Silverved</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverved</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128815352</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>752743</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7094781</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128815353</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>752794</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7094682</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128815359</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>752797</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7094712</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128815357</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>752752</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7094775</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Silverlåga 2delad norra delen</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128815358</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92814</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>752797</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7094712</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Även spadskinn under samma låga</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128815354</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92814</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>752754</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7094754</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Under silverlåga,kollekt insamlat</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B2" t="n">
-        <v>91655</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R2" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -903,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B4" t="n">
-        <v>92788</v>
+        <v>91655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R4" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92788</v>
+        <v>92814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R12" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92814</v>
+        <v>92788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R13" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2657,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815356</v>
+        <v>128815353</v>
       </c>
       <c r="B21" t="n">
-        <v>92810</v>
+        <v>57876</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,26 +2668,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2695,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752793</v>
+        <v>752794</v>
       </c>
       <c r="R21" t="n">
-        <v>7094748</v>
+        <v>7094682</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2733,40 +2738,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Silverved</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Silverved</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2885,42 +2864,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128815353</v>
+        <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>92768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6055</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2928,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752794</v>
+        <v>752797</v>
       </c>
       <c r="R23" t="n">
-        <v>7094682</v>
+        <v>7094712</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2966,12 +2940,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2990,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128815359</v>
+        <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92768</v>
+        <v>92788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,37 +2981,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6055</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752797</v>
+        <v>752752</v>
       </c>
       <c r="R24" t="n">
-        <v>7094712</v>
+        <v>7094775</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3068,7 +3045,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+          <t>Silverlåga 2delad norra delen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,7 +3054,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3096,45 +3072,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128815357</v>
+        <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92788</v>
+        <v>92810</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752752</v>
+        <v>752793</v>
       </c>
       <c r="R25" t="n">
-        <v>7094775</v>
+        <v>7094748</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3171,7 +3150,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Silverlåga 2delad norra delen</t>
+          <t>Kollekt insamlat. Kollekt202509005</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3180,8 +3159,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Silverved</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverved</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Även spadskinn under samma låga</t>
+          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Under silverlåga,kollekt insamlat</t>
+          <t>Under silverlåga. Kollekt insamlat kollekt202509004</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128787957</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128787996</v>
       </c>
       <c r="B4" t="n">
-        <v>91655</v>
+        <v>91660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815353</v>
+        <v>128815352</v>
       </c>
       <c r="B21" t="n">
         <v>57876</v>
@@ -2686,24 +2686,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752794</v>
+        <v>752743</v>
       </c>
       <c r="R21" t="n">
-        <v>7094682</v>
+        <v>7094781</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2762,7 +2759,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815352</v>
+        <v>128815353</v>
       </c>
       <c r="B22" t="n">
         <v>57876</v>
@@ -2791,21 +2788,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752743</v>
+        <v>752794</v>
       </c>
       <c r="R22" t="n">
-        <v>7094781</v>
+        <v>7094682</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92768</v>
+        <v>92773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>91665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R2" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,7 +800,7 @@
         <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B4" t="n">
-        <v>91660</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R4" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92819</v>
+        <v>92825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92819</v>
+        <v>92825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787943</v>
+        <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>90327</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752782</v>
+        <v>752711</v>
       </c>
       <c r="R3" t="n">
-        <v>7094651</v>
+        <v>7094778</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>90327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +910,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R4" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92825</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R13" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -2657,7 +2657,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815352</v>
+        <v>128815353</v>
       </c>
       <c r="B21" t="n">
         <v>57876</v>
@@ -2686,21 +2686,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752743</v>
+        <v>752794</v>
       </c>
       <c r="R21" t="n">
-        <v>7094781</v>
+        <v>7094682</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2759,7 +2762,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815353</v>
+        <v>128815352</v>
       </c>
       <c r="B22" t="n">
         <v>57876</v>
@@ -2788,24 +2791,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752794</v>
+        <v>752743</v>
       </c>
       <c r="R22" t="n">
-        <v>7094682</v>
+        <v>7094781</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B2" t="n">
-        <v>91665</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R2" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>91669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,7 +902,7 @@
         <v>128787943</v>
       </c>
       <c r="B4" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128787945</v>
       </c>
       <c r="B11" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92825</v>
+        <v>92829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815353</v>
+        <v>128815352</v>
       </c>
       <c r="B21" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2686,24 +2686,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752794</v>
+        <v>752743</v>
       </c>
       <c r="R21" t="n">
-        <v>7094682</v>
+        <v>7094781</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2762,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815352</v>
+        <v>128815353</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2791,21 +2788,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752743</v>
+        <v>752794</v>
       </c>
       <c r="R22" t="n">
-        <v>7094781</v>
+        <v>7094682</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92778</v>
+        <v>92782</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92820</v>
+        <v>92824</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92825</v>
+        <v>92829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92825</v>
+        <v>92829</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>92802</v>
+        <v>91669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R2" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>91669</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R3" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,26 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B7" t="n">
         <v>92802</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R7" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B8" t="n">
         <v>92802</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R8" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2045,7 +2045,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787966</v>
+        <v>128787967</v>
       </c>
       <c r="B15" t="n">
         <v>92802</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752758</v>
+        <v>752787</v>
       </c>
       <c r="R15" t="n">
-        <v>7094712</v>
+        <v>7094681</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,7 +2147,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B16" t="n">
         <v>92802</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R16" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>90331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +808,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787943</v>
+        <v>128787957</v>
       </c>
       <c r="B4" t="n">
-        <v>90331</v>
+        <v>92802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,38 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752782</v>
+        <v>752711</v>
       </c>
       <c r="R4" t="n">
-        <v>7094651</v>
+        <v>7094778</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B7" t="n">
         <v>92802</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R7" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B8" t="n">
         <v>92802</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R8" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2045,7 +2045,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B15" t="n">
         <v>92802</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R15" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,7 +2147,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787966</v>
+        <v>128787967</v>
       </c>
       <c r="B16" t="n">
         <v>92802</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752758</v>
+        <v>752787</v>
       </c>
       <c r="R16" t="n">
-        <v>7094712</v>
+        <v>7094681</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128787957</v>
       </c>
       <c r="B4" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128787945</v>
       </c>
       <c r="B11" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815352</v>
+        <v>128815353</v>
       </c>
       <c r="B21" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2686,21 +2686,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752743</v>
+        <v>752794</v>
       </c>
       <c r="R21" t="n">
-        <v>7094781</v>
+        <v>7094682</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2759,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815353</v>
+        <v>128815352</v>
       </c>
       <c r="B22" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,24 +2791,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752794</v>
+        <v>752743</v>
       </c>
       <c r="R22" t="n">
-        <v>7094682</v>
+        <v>7094781</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92782</v>
+        <v>92787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92815</v>
+        <v>92842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R12" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92842</v>
+        <v>92815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R13" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B2" t="n">
-        <v>91681</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R2" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>92815</v>
+        <v>90346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787943</v>
+        <v>128787996</v>
       </c>
       <c r="B4" t="n">
-        <v>90343</v>
+        <v>91684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,38 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752782</v>
+        <v>752756</v>
       </c>
       <c r="R4" t="n">
-        <v>7094651</v>
+        <v>7094697</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90343</v>
+        <v>90346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90343</v>
+        <v>90346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92795</v>
+        <v>92800</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>90349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R2" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787943</v>
+        <v>128787996</v>
       </c>
       <c r="B3" t="n">
-        <v>90346</v>
+        <v>91687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,38 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752782</v>
+        <v>752756</v>
       </c>
       <c r="R3" t="n">
-        <v>7094651</v>
+        <v>7094697</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,6 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -883,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B4" t="n">
-        <v>91684</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R4" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90346</v>
+        <v>90349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92847</v>
+        <v>92823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92820</v>
+        <v>92850</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R13" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90346</v>
+        <v>90349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92800</v>
+        <v>92803</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92847</v>
+        <v>92850</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92847</v>
+        <v>92850</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787943</v>
+        <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>90349</v>
+        <v>91687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752782</v>
+        <v>752756</v>
       </c>
       <c r="R2" t="n">
-        <v>7094651</v>
+        <v>7094697</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>91687</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R3" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>90349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +910,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R4" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B7" t="n">
         <v>92823</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R7" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B8" t="n">
         <v>92823</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R8" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B7" t="n">
         <v>92823</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R7" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B8" t="n">
         <v>92823</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R8" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92823</v>
+        <v>92850</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R12" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92850</v>
+        <v>92823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R13" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787996</v>
+        <v>128787957</v>
       </c>
       <c r="B2" t="n">
-        <v>91687</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752756</v>
+        <v>752711</v>
       </c>
       <c r="R2" t="n">
-        <v>7094697</v>
+        <v>7094778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>90349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787943</v>
+        <v>128787996</v>
       </c>
       <c r="B4" t="n">
-        <v>90349</v>
+        <v>91687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,38 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752782</v>
+        <v>752756</v>
       </c>
       <c r="R4" t="n">
-        <v>7094651</v>
+        <v>7094697</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92850</v>
+        <v>92823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92823</v>
+        <v>92850</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R13" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>91694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R2" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787943</v>
+        <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>90349</v>
+        <v>92830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,38 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752782</v>
+        <v>752711</v>
       </c>
       <c r="R3" t="n">
-        <v>7094651</v>
+        <v>7094778</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787996</v>
+        <v>128787943</v>
       </c>
       <c r="B4" t="n">
-        <v>91687</v>
+        <v>90353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,34 +910,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>6286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752756</v>
+        <v>752782</v>
       </c>
       <c r="R4" t="n">
-        <v>7094697</v>
+        <v>7094651</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90349</v>
+        <v>90353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128787945</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92823</v>
+        <v>92857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R12" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92850</v>
+        <v>92830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R13" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90349</v>
+        <v>90353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>128815352</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128815353</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92803</v>
+        <v>92810</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92845</v>
+        <v>92852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92850</v>
+        <v>92857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92850</v>
+        <v>92857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -2045,7 +2045,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787966</v>
+        <v>128787967</v>
       </c>
       <c r="B15" t="n">
         <v>92830</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752758</v>
+        <v>752787</v>
       </c>
       <c r="R15" t="n">
-        <v>7094712</v>
+        <v>7094681</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,7 +2147,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B16" t="n">
         <v>92830</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R16" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128787943</v>
       </c>
       <c r="B4" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B7" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R7" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B8" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R8" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92857</v>
+        <v>92837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92830</v>
+        <v>92864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R13" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787967</v>
       </c>
       <c r="B15" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787966</v>
       </c>
       <c r="B16" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92810</v>
+        <v>92817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92852</v>
+        <v>92859</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128787943</v>
       </c>
       <c r="B4" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R7" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787964</v>
+        <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R8" t="n">
-        <v>7094671</v>
+        <v>7094654</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128787945</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128787973</v>
       </c>
       <c r="B12" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128787946</v>
       </c>
       <c r="B13" t="n">
-        <v>92864</v>
+        <v>92866</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R15" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787966</v>
+        <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752758</v>
+        <v>752787</v>
       </c>
       <c r="R16" t="n">
-        <v>7094712</v>
+        <v>7094681</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>128815352</v>
       </c>
       <c r="B21" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128815353</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92864</v>
+        <v>92866</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92864</v>
+        <v>92866</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>128787943</v>
       </c>
       <c r="B3" t="n">
-        <v>92839</v>
+        <v>90362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +808,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752782</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787943</v>
+        <v>128787957</v>
       </c>
       <c r="B4" t="n">
-        <v>90362</v>
+        <v>92839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,38 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752782</v>
+        <v>752711</v>
       </c>
       <c r="R4" t="n">
-        <v>7094651</v>
+        <v>7094778</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787996</v>
+        <v>128787943</v>
       </c>
       <c r="B2" t="n">
-        <v>91703</v>
+        <v>90363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>6286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752756</v>
+        <v>752782</v>
       </c>
       <c r="R2" t="n">
-        <v>7094697</v>
+        <v>7094651</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +765,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787943</v>
+        <v>128787957</v>
       </c>
       <c r="B3" t="n">
-        <v>90362</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752782</v>
+        <v>752711</v>
       </c>
       <c r="R3" t="n">
-        <v>7094651</v>
+        <v>7094778</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787957</v>
+        <v>128787996</v>
       </c>
       <c r="B4" t="n">
-        <v>92839</v>
+        <v>91712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752711</v>
+        <v>752756</v>
       </c>
       <c r="R4" t="n">
-        <v>7094778</v>
+        <v>7094697</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>128787959</v>
       </c>
       <c r="B5" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128787969</v>
       </c>
       <c r="B6" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128787964</v>
       </c>
       <c r="B7" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128787972</v>
       </c>
       <c r="B8" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>128787961</v>
       </c>
       <c r="B9" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128787944</v>
       </c>
       <c r="B10" t="n">
-        <v>90362</v>
+        <v>90363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787973</v>
+        <v>128787946</v>
       </c>
       <c r="B12" t="n">
-        <v>92839</v>
+        <v>92852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752821</v>
+        <v>752779</v>
       </c>
       <c r="R12" t="n">
-        <v>7094673</v>
+        <v>7094659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787946</v>
+        <v>128787973</v>
       </c>
       <c r="B13" t="n">
-        <v>92866</v>
+        <v>92825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752779</v>
+        <v>752821</v>
       </c>
       <c r="R13" t="n">
-        <v>7094659</v>
+        <v>7094673</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,7 +1942,7 @@
         <v>128787940</v>
       </c>
       <c r="B14" t="n">
-        <v>90362</v>
+        <v>90363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128787966</v>
       </c>
       <c r="B15" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>128787967</v>
       </c>
       <c r="B16" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128787956</v>
       </c>
       <c r="B17" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128787971</v>
       </c>
       <c r="B18" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>92805</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92861</v>
+        <v>92847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92866</v>
+        <v>92852</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92866</v>
+        <v>92852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -2456,7 +2456,7 @@
         <v>128815360</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>92805</v>
+        <v>92806</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128815357</v>
       </c>
       <c r="B24" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92847</v>
+        <v>92848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92852</v>
+        <v>92853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92852</v>
+        <v>92853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>92848</v>
+        <v>92851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>92853</v>
+        <v>92856</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>92853</v>
+        <v>92856</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93036</v>
+        <v>93039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93041</v>
+        <v>93044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93041</v>
+        <v>93044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93039</v>
+        <v>93065</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93044</v>
+        <v>93070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93044</v>
+        <v>93070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93065</v>
+        <v>93066</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93070</v>
+        <v>93071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93070</v>
+        <v>93071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93066</v>
+        <v>93067</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93071</v>
+        <v>93072</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93071</v>
+        <v>93072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93067</v>
+        <v>93069</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93072</v>
+        <v>93074</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93072</v>
+        <v>93074</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93069</v>
+        <v>93073</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93074</v>
+        <v>93078</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93074</v>
+        <v>93078</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93073</v>
+        <v>93086</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93078</v>
+        <v>93091</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93078</v>
+        <v>93091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93086</v>
+        <v>93087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93091</v>
+        <v>93092</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93091</v>
+        <v>93092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -3075,7 +3075,7 @@
         <v>128815356</v>
       </c>
       <c r="B25" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128815358</v>
       </c>
       <c r="B26" t="n">
-        <v>93092</v>
+        <v>93093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128815354</v>
       </c>
       <c r="B27" t="n">
-        <v>93092</v>
+        <v>93093</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128787943</v>
+        <v>128787996</v>
       </c>
       <c r="B2" t="n">
-        <v>90363</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752782</v>
+        <v>752756</v>
       </c>
       <c r="R2" t="n">
-        <v>7094651</v>
+        <v>7094697</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,17 +750,37 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Kollekt insamlat</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,48 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128787957</v>
+        <v>61126685</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752711</v>
+        <v>752731</v>
       </c>
       <c r="R3" t="n">
-        <v>7094778</v>
+        <v>7094719</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,17 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787996</v>
+        <v>128787956</v>
       </c>
       <c r="B4" t="n">
-        <v>91712</v>
+        <v>93201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752756</v>
+        <v>752794</v>
       </c>
       <c r="R4" t="n">
-        <v>7094697</v>
+        <v>7094637</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,37 +969,17 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kollekt insamlat</t>
+          <t>Under silverved just bredvid parkeringen</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128787959</v>
+        <v>128787957</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752779</v>
+        <v>752711</v>
       </c>
       <c r="R5" t="n">
-        <v>7094692</v>
+        <v>7094778</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>under silverlåga, delvis nedbruten, halvvägs i mossa</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128787969</v>
+        <v>128787959</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752776</v>
+        <v>752779</v>
       </c>
       <c r="R6" t="n">
-        <v>7094659</v>
+        <v>7094692</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1182,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Talllåga kort, vid grusväg</t>
+          <t>under silverlåga, delvis nedbruten, halvvägs i mossa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787964</v>
+        <v>128787961</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R7" t="n">
-        <v>7094671</v>
+        <v>7094672</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under kortare silverlåga, ganska nära lång silverlåga som har smalfotad taggsvamp också</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787972</v>
+        <v>128787964</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752808</v>
+        <v>752791</v>
       </c>
       <c r="R8" t="n">
-        <v>7094654</v>
+        <v>7094671</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1386,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128787961</v>
+        <v>128787966</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752808</v>
+        <v>752758</v>
       </c>
       <c r="R9" t="n">
-        <v>7094672</v>
+        <v>7094712</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1488,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Under kortare silverlåga, ganska nära lång silverlåga som har smalfotad taggsvamp också</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128787944</v>
+        <v>128787967</v>
       </c>
       <c r="B10" t="n">
-        <v>90363</v>
+        <v>93201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,38 +1517,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752769</v>
+        <v>752787</v>
       </c>
       <c r="R10" t="n">
-        <v>7094680</v>
+        <v>7094681</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1590,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,57 +1608,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128787945</v>
+        <v>128787969</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752784</v>
+        <v>752776</v>
       </c>
       <c r="R11" t="n">
-        <v>7094657</v>
+        <v>7094659</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1696,19 +1676,14 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Talllåga kort, vid grusväg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787946</v>
+        <v>128787971</v>
       </c>
       <c r="B12" t="n">
-        <v>92852</v>
+        <v>93201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752779</v>
+        <v>752800</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094653</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,7 +1785,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>Under tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787973</v>
+        <v>128787972</v>
       </c>
       <c r="B13" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752821</v>
+        <v>752808</v>
       </c>
       <c r="R13" t="n">
-        <v>7094673</v>
+        <v>7094654</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128787940</v>
+        <v>128787973</v>
       </c>
       <c r="B14" t="n">
-        <v>90363</v>
+        <v>93201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,38 +1925,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752757</v>
+        <v>752821</v>
       </c>
       <c r="R14" t="n">
-        <v>7094726</v>
+        <v>7094673</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2018,7 +1989,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växte mellan 2 äldre silverlågor</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787966</v>
+        <v>128815357</v>
       </c>
       <c r="B15" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752758</v>
+        <v>752752</v>
       </c>
       <c r="R15" t="n">
-        <v>7094712</v>
+        <v>7094775</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2110,17 +2081,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Silverlåga 2delad norra delen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128787967</v>
+        <v>128815360</v>
       </c>
       <c r="B16" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752787</v>
+        <v>752738</v>
       </c>
       <c r="R16" t="n">
-        <v>7094681</v>
+        <v>7094815</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2212,17 +2183,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>tunn tallgren nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128787956</v>
+        <v>128815361</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752794</v>
+        <v>752840</v>
       </c>
       <c r="R17" t="n">
-        <v>7094637</v>
+        <v>7094744</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2314,17 +2285,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Under silverved just bredvid parkeringen</t>
+          <t>silverlåga rotvälta</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128787971</v>
+        <v>128815362</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752800</v>
+        <v>752811</v>
       </c>
       <c r="R18" t="n">
-        <v>7094653</v>
+        <v>7094687</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2416,17 +2387,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Under tallåga</t>
+          <t>silverlåga nedbruten delvis</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2453,48 +2424,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128815360</v>
+        <v>61126684</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752738</v>
+        <v>752685</v>
       </c>
       <c r="R19" t="n">
-        <v>7094815</v>
+        <v>7094814</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2518,17 +2489,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>tunn tallgren nedsänkt i mossa</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,57 +2509,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128815362</v>
+        <v>128815356</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>93223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752811</v>
+        <v>752793</v>
       </c>
       <c r="R20" t="n">
-        <v>7094687</v>
+        <v>7094748</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2630,7 +2599,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>silverlåga nedbruten delvis</t>
+          <t>Kollekt insamlat. Kollekt202509005 Artbestämd av Sten Svantesson 20251227</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2639,10 +2608,40 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AT20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Silverved</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverved</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW20" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -2657,50 +2656,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815352</v>
+        <v>128815359</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>93181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6055</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752743</v>
+        <v>752797</v>
       </c>
       <c r="R21" t="n">
-        <v>7094781</v>
+        <v>7094712</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2735,12 +2732,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2759,53 +2762,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815353</v>
+        <v>128787940</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>90710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752794</v>
+        <v>752757</v>
       </c>
       <c r="R22" t="n">
-        <v>7094682</v>
+        <v>7094726</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2832,12 +2831,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växte mellan 2 äldre silverlågor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128815359</v>
+        <v>128787943</v>
       </c>
       <c r="B23" t="n">
-        <v>92806</v>
+        <v>90710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,37 +2879,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6055</v>
+        <v>6286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752797</v>
+        <v>752782</v>
       </c>
       <c r="R23" t="n">
-        <v>7094712</v>
+        <v>7094651</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2932,17 +2937,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,7 +2956,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2970,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128815357</v>
+        <v>128787944</v>
       </c>
       <c r="B24" t="n">
-        <v>92826</v>
+        <v>90710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,34 +2985,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752752</v>
+        <v>752769</v>
       </c>
       <c r="R24" t="n">
-        <v>7094775</v>
+        <v>7094680</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3035,17 +3043,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Silverlåga 2delad norra delen</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3072,10 +3075,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128815356</v>
+        <v>128787945</v>
       </c>
       <c r="B25" t="n">
-        <v>93088</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3083,26 +3086,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3110,10 +3122,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752793</v>
+        <v>752784</v>
       </c>
       <c r="R25" t="n">
-        <v>7094748</v>
+        <v>7094657</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3140,17 +3152,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat. Kollekt202509005 Artbestämd av Sten Svantesson 20251227</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,40 +3176,10 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Silverved</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Silverved</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -3207,48 +3194,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128815358</v>
+        <v>128815352</v>
       </c>
       <c r="B26" t="n">
-        <v>93093</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>232140</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752797</v>
+        <v>752743</v>
       </c>
       <c r="R26" t="n">
-        <v>7094712</v>
+        <v>7094781</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3283,31 +3272,16 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga Artbestämd av Sten Svantesson 20251227</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -3322,37 +3296,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128815354</v>
+        <v>128815353</v>
       </c>
       <c r="B27" t="n">
-        <v>93093</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>232140</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3360,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752754</v>
+        <v>752794</v>
       </c>
       <c r="R27" t="n">
-        <v>7094754</v>
+        <v>7094682</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3398,42 +3377,481 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128787974</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>752825</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7094640</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Vilar på silverlåga</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128787946</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>752779</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7094659</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Under silverved, grövre tallgren</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128815354</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>752754</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7094754</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>Under silverlåga. Kollekt insamlat kollekt202509004 Artbestämd av Sten Svantesson 20251227</t>
         </is>
       </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="inlineStr">
         <is>
           <t>Sten Svantesson</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="AT30" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128815358</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>752797</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7094712</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga Artbestämd av Sten Svantesson 20251227</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61126685</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787956</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787961</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787964</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787966</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787967</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787969</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787971</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787972</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787973</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815357</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815360</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815361</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815362</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2518,6 +2608,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61126684</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2653,6 +2748,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815356</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,6 +2859,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815359</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2865,6 +2970,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787940</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2971,6 +3081,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787943</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3072,6 +3187,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787944</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3191,6 +3311,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787945</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3293,6 +3418,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815352</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3398,6 +3528,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815353</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3520,6 +3655,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787974</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3622,6 +3762,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787946</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3737,6 +3882,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815354</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3852,8 +4002,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815358</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>